--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108572</v>
+        <v>120108575</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>94574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,7 +843,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580070</v>
+        <v>580068</v>
       </c>
       <c r="R3" t="n">
         <v>6508783</v>
@@ -877,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108575</v>
+        <v>120108581</v>
       </c>
       <c r="B4" t="n">
-        <v>94574</v>
+        <v>105009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,29 +931,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -962,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580068</v>
+        <v>580081</v>
       </c>
       <c r="R4" t="n">
-        <v>6508783</v>
+        <v>6508670</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B5" t="n">
-        <v>105009</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,35 +1047,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R5" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108580</v>
+        <v>120108581</v>
       </c>
       <c r="B2" t="n">
         <v>105009</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>580081</v>
       </c>
       <c r="R2" t="n">
-        <v>6508681</v>
+        <v>6508670</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108575</v>
+        <v>120108580</v>
       </c>
       <c r="B3" t="n">
-        <v>94574</v>
+        <v>105009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,29 +811,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580068</v>
+        <v>580081</v>
       </c>
       <c r="R3" t="n">
-        <v>6508783</v>
+        <v>6508681</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108581</v>
+        <v>120108575</v>
       </c>
       <c r="B4" t="n">
-        <v>105009</v>
+        <v>94574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,29 +931,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580081</v>
+        <v>580068</v>
       </c>
       <c r="R4" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B2" t="n">
-        <v>105009</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R2" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +797,7 @@
         <v>120108580</v>
       </c>
       <c r="B3" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -918,7 +917,7 @@
         <v>120108575</v>
       </c>
       <c r="B4" t="n">
-        <v>94574</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108572</v>
+        <v>120108581</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>105032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1046,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580070</v>
+        <v>580081</v>
       </c>
       <c r="R5" t="n">
-        <v>6508783</v>
+        <v>6508670</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108572</v>
+        <v>120108580</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580070</v>
+        <v>580081</v>
       </c>
       <c r="R2" t="n">
-        <v>6508783</v>
+        <v>6508681</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108580</v>
+        <v>120108581</v>
       </c>
       <c r="B3" t="n">
         <v>105032</v>
@@ -829,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -845,7 +846,7 @@
         <v>580081</v>
       </c>
       <c r="R3" t="n">
-        <v>6508681</v>
+        <v>6508670</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B5" t="n">
-        <v>105032</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,35 +1047,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R5" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108575</v>
+        <v>120108572</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +927,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,7 +962,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580068</v>
+        <v>580070</v>
       </c>
       <c r="R4" t="n">
         <v>6508783</v>
@@ -998,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108572</v>
+        <v>120108575</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1046,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580070</v>
+        <v>580068</v>
       </c>
       <c r="R5" t="n">
         <v>6508783</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108580</v>
+        <v>120108581</v>
       </c>
       <c r="B2" t="n">
         <v>105032</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -726,7 +726,7 @@
         <v>580081</v>
       </c>
       <c r="R2" t="n">
-        <v>6508681</v>
+        <v>6508670</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +807,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R3" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108572</v>
+        <v>120108575</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,34 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580070</v>
+        <v>580068</v>
       </c>
       <c r="R4" t="n">
         <v>6508783</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108575</v>
+        <v>120108580</v>
       </c>
       <c r="B5" t="n">
-        <v>94597</v>
+        <v>105032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,29 +1050,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580068</v>
+        <v>580081</v>
       </c>
       <c r="R5" t="n">
-        <v>6508783</v>
+        <v>6508681</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,6 +1151,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120482903</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580060</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6508683</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108572</v>
+        <v>120108575</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>94597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,7 +843,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580070</v>
+        <v>580068</v>
       </c>
       <c r="R3" t="n">
         <v>6508783</v>
@@ -877,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108575</v>
+        <v>120108572</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +927,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580068</v>
+        <v>580070</v>
       </c>
       <c r="R4" t="n">
         <v>6508783</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R2" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108575</v>
+        <v>120108581</v>
       </c>
       <c r="B3" t="n">
-        <v>94597</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,29 +810,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580068</v>
+        <v>580081</v>
       </c>
       <c r="R3" t="n">
-        <v>6508783</v>
+        <v>6508670</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108572</v>
+        <v>120108580</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>105032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,34 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580070</v>
+        <v>580081</v>
       </c>
       <c r="R4" t="n">
-        <v>6508783</v>
+        <v>6508681</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120108580</v>
+        <v>120108575</v>
       </c>
       <c r="B5" t="n">
-        <v>105032</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,29 +1050,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580081</v>
+        <v>580068</v>
       </c>
       <c r="R5" t="n">
-        <v>6508681</v>
+        <v>6508783</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40489-2024 artfynd.xlsx
+++ b/artfynd/A 40489-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120108572</v>
+        <v>120108580</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580070</v>
+        <v>580081</v>
       </c>
       <c r="R2" t="n">
-        <v>6508783</v>
+        <v>6508681</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120108581</v>
+        <v>120108572</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +807,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580081</v>
+        <v>580070</v>
       </c>
       <c r="R3" t="n">
-        <v>6508670</v>
+        <v>6508783</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120108580</v>
+        <v>120108581</v>
       </c>
       <c r="B4" t="n">
         <v>105032</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -965,7 +965,7 @@
         <v>580081</v>
       </c>
       <c r="R4" t="n">
-        <v>6508681</v>
+        <v>6508670</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
